--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CC4BA7-3550-4C58-BAE5-2F4F0510B2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F729001-4DDE-403A-8D7C-084FA7626AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Donor</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>Talia Feldman</t>
+  </si>
+  <si>
+    <t>Mark Lione</t>
+  </si>
+  <si>
+    <t>Don Halpern</t>
   </si>
 </sst>
 </file>
@@ -471,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
@@ -574,6 +580,22 @@
         <v>118</v>
       </c>
     </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F729001-4DDE-403A-8D7C-084FA7626AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2E30A5-ECD2-4BB9-918B-933CE34B9EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
+    <workbookView xWindow="11750" yWindow="2580" windowWidth="7660" windowHeight="10730" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Donor</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>Don Halpern</t>
+  </si>
+  <si>
+    <t>Cindy Siegel</t>
+  </si>
+  <si>
+    <t>Ronen Feldman</t>
+  </si>
+  <si>
+    <t>Derek Chiari</t>
+  </si>
+  <si>
+    <t>Ted &amp; Bethe Halpern</t>
   </si>
 </sst>
 </file>
@@ -477,10 +489,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -596,6 +608,38 @@
         <v>250</v>
       </c>
     </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2E30A5-ECD2-4BB9-918B-933CE34B9EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8CF2BF-C8A8-4218-9E03-AF31028212A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11750" yWindow="2580" windowWidth="7660" windowHeight="10730" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
+    <workbookView xWindow="10480" yWindow="2470" windowWidth="7660" windowHeight="10730" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Donor</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>Ted &amp; Bethe Halpern</t>
+  </si>
+  <si>
+    <t>Reynolds American Inc.</t>
+  </si>
+  <si>
+    <t>Verisign, Inc.</t>
   </si>
 </sst>
 </file>
@@ -489,10 +495,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -640,6 +646,22 @@
         <v>2500</v>
       </c>
     </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8CF2BF-C8A8-4218-9E03-AF31028212A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6E0B95-D427-4AE1-9ABE-82322BB0B9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10480" yWindow="2470" windowWidth="7660" windowHeight="10730" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
+    <workbookView xWindow="6870" yWindow="2810" windowWidth="7660" windowHeight="10730" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Donor</t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>Verisign, Inc.</t>
+  </si>
+  <si>
+    <t>Julie Collier</t>
+  </si>
+  <si>
+    <t>Janine Rendano</t>
   </si>
 </sst>
 </file>
@@ -495,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
@@ -662,6 +668,22 @@
         <v>500</v>
       </c>
     </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6E0B95-D427-4AE1-9ABE-82322BB0B9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC4DC5C-A17E-4628-8156-BD146CBA32AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6870" yWindow="2810" windowWidth="7660" windowHeight="10730" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
+    <workbookView xWindow="10880" yWindow="3450" windowWidth="7660" windowHeight="10730" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Donor</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Janine Rendano</t>
+  </si>
+  <si>
+    <t>Andi Maatallah</t>
   </si>
 </sst>
 </file>
@@ -501,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
@@ -684,6 +687,14 @@
         <v>200</v>
       </c>
     </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC4DC5C-A17E-4628-8156-BD146CBA32AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57605119-B28C-4F00-8964-EBA2377A1E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10880" yWindow="3450" windowWidth="7660" windowHeight="10730" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Donor</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>Andi Maatallah</t>
+  </si>
+  <si>
+    <t>ECAD Match</t>
+  </si>
+  <si>
+    <t>Sol Botbol</t>
   </si>
 </sst>
 </file>
@@ -504,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
@@ -695,6 +701,22 @@
         <v>100</v>
       </c>
     </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTN_2026_Donations.xlsx
+++ b/LTN_2026_Donations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackH\Documents\Blood Cancer United\LTN_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57605119-B28C-4F00-8964-EBA2377A1E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B85E44F-C943-4933-9384-5EBC4E2A792D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10880" yWindow="3450" windowWidth="7660" windowHeight="10730" xr2:uid="{82F9E51D-9C08-4048-BCB4-3512E8A00433}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Donor</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>Sol Botbol</t>
+  </si>
+  <si>
+    <t>Steven Singer</t>
+  </si>
+  <si>
+    <t>Eric Markowitz</t>
   </si>
 </sst>
 </file>
@@ -510,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825204A-042E-49AE-8958-CC460986F1C1}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
@@ -717,6 +723,22 @@
         <v>250</v>
       </c>
     </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
